--- a/archive/2026/05/NASDAQ_Breakout_Screener_2026-05-13.xlsx
+++ b/archive/2026/05/NASDAQ_Breakout_Screener_2026-05-13.xlsx
@@ -1805,11 +1805,7 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>674M</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
         <v>16.92000007629395</v>
       </c>
@@ -1912,7 +1908,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AXSM</t>
+          <t>ASRT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1922,61 +1918,61 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11.53B</t>
+          <t>146M</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.0299987792969</v>
+        <v>22.54999923706055</v>
       </c>
       <c r="E3" t="n">
-        <v>3.49</v>
+        <v>0.85</v>
       </c>
       <c r="F3" t="n">
-        <v>224.0299987792969</v>
+        <v>22.54999923706055</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8855138161408768</v>
+        <v>0.4156742911068171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TBRG</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>388M</t>
+          <t>5.44B</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.88999938964844</v>
+        <v>87.06999969482422</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="F4" t="n">
-        <v>25.88999938964844</v>
+        <v>87.06999969482422</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3748401844174964</v>
+        <v>0.9654082846518192</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STRO</t>
+          <t>AVR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1986,445 +1982,445 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>678M</t>
+          <t>651M</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.90999984741211</v>
+        <v>6.699999809265137</v>
       </c>
       <c r="E5" t="n">
-        <v>4.07</v>
+        <v>2.92</v>
       </c>
       <c r="F5" t="n">
-        <v>40.90999984741211</v>
+        <v>6.699999809265137</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9666095964071547</v>
+        <v>0.6323937556144499</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>TBRG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13.87B</t>
+          <t>388M</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>87.31999969482422</v>
+        <v>25.88999938964844</v>
       </c>
       <c r="E6" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>87.31999969482422</v>
+        <v>25.88999938964844</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9940948807500036</v>
+        <v>0.3748401844174964</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>STRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>121.47B</t>
+          <t>678M</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>106.5800018310547</v>
+        <v>40.90999984741211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.79</v>
+        <v>4.07</v>
       </c>
       <c r="F7" t="n">
-        <v>106.5800018310547</v>
+        <v>40.90999984741211</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8139188682459479</v>
+        <v>0.9666095964071547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBRA</t>
+          <t>SSRM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.29B</t>
+          <t>7.42B</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.96999931335449</v>
+        <v>35.7400016784668</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4</v>
+        <v>2.88</v>
       </c>
       <c r="F8" t="n">
-        <v>20.96999931335449</v>
+        <v>35.7400016784668</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6378609424012992</v>
+        <v>1.0087672624617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>QUMS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.11B</t>
+          <t>116M</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.34000015258789</v>
+        <v>10.17000007629395</v>
       </c>
       <c r="E9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>27.34000015258789</v>
+        <v>10.17000007629395</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8239878956170887</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUMS</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>116M</t>
+          <t>121.47B</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.17000007629395</v>
+        <v>106.5800018310547</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="F10" t="n">
-        <v>10.17000007629395</v>
+        <v>106.5800018310547</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.8139188682459479</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SSRM</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.42B</t>
+          <t>406M</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35.7400016784668</v>
+        <v>250.6499938964844</v>
       </c>
       <c r="E11" t="n">
-        <v>2.88</v>
+        <v>4.35</v>
       </c>
       <c r="F11" t="n">
-        <v>35.7400016784668</v>
+        <v>250.6499938964844</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0087672624617</v>
+        <v>0.5244755244755245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NOEM</t>
+          <t>PHVS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>100M</t>
+          <t>2.20B</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.44999980926514</v>
+        <v>31.25</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="F12" t="n">
-        <v>10.44999980926514</v>
+        <v>31.25</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02613695765812859</v>
+        <v>1.199478001491424</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NESR</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.71B</t>
+          <t>3.11B</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.84000015258789</v>
+        <v>27.34000015258789</v>
       </c>
       <c r="E13" t="n">
-        <v>5.54</v>
+        <v>2.24</v>
       </c>
       <c r="F13" t="n">
-        <v>26.84000015258789</v>
+        <v>27.34000015258789</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8909203522945157</v>
+        <v>0.8239878956170887</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OLPX</t>
+          <t>SBRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.37B</t>
+          <t>5.29B</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.039999961853027</v>
+        <v>20.96999931335449</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="F14" t="n">
-        <v>2.039999961853027</v>
+        <v>20.96999931335449</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.714448430203208</v>
+        <v>0.6378609424012992</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORIQ</t>
+          <t>AXSM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>88M</t>
+          <t>11.53B</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.25</v>
+        <v>224.0299987792969</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="F15" t="n">
-        <v>10.25</v>
+        <v>224.0299987792969</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1855287569573284</v>
+        <v>0.8855138161408768</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PHVS</t>
+          <t>SOLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.20B</t>
+          <t>13.87B</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31.25</v>
+        <v>87.31999969482422</v>
       </c>
       <c r="E16" t="n">
-        <v>4.34</v>
+        <v>2.22</v>
       </c>
       <c r="F16" t="n">
-        <v>31.25</v>
+        <v>87.31999969482422</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.199478001491424</v>
+        <v>0.9940948807500036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>406M</t>
+          <t>309M</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>250.6499938964844</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="E17" t="n">
-        <v>4.35</v>
+        <v>1.84</v>
       </c>
       <c r="F17" t="n">
-        <v>250.6499938964844</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5244755244755245</v>
+        <v>1.083318654218778</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NDLS</t>
+          <t>INAC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>76M</t>
+          <t>151M</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.94999980926514</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="E18" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>12.94999980926514</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8650909165453763</v>
+        <v>0.8087535680304472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>KALV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2434,61 +2430,61 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15.67B</t>
+          <t>1.42B</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>155.8000030517578</v>
+        <v>26.72999954223633</v>
       </c>
       <c r="E19" t="n">
-        <v>3.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>155.8000030517578</v>
+        <v>26.72999954223633</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.147435268389105</v>
+        <v>0.699942073759413</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KALV</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.42B</t>
+          <t>13.66B</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.72999954223633</v>
+        <v>685.47998046875</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="F20" t="n">
-        <v>26.72999954223633</v>
+        <v>685.47998046875</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.699942073759413</v>
+        <v>0.6747409728692019</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INAC</t>
+          <t>FSHP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2498,281 +2494,281 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>151M</t>
+          <t>55M</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.19999980926514</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F21" t="n">
-        <v>10.19999980926514</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8087535680304472</v>
+        <v>0.1908396946564886</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FITBI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>5.37T</t>
-        </is>
-      </c>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>220.7799987792969</v>
+        <v>25.45999908447266</v>
       </c>
       <c r="E22" t="n">
-        <v>0.61</v>
+        <v>0.08</v>
       </c>
       <c r="F22" t="n">
-        <v>220.7799987792969</v>
+        <v>25.45999908447266</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9761118533538271</v>
+        <v>0.6218015737632752</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LCCC</t>
+          <t>GSAT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>92M</t>
+          <t>10.65B</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.35000038146973</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="F23" t="n">
-        <v>10.35000038146973</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.7662014091676267</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FITBI</t>
+          <t>GLNG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5.84B</t>
+        </is>
+      </c>
       <c r="D24" t="n">
-        <v>25.45999908447266</v>
+        <v>57.36000061035156</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08</v>
+        <v>0.95</v>
       </c>
       <c r="F24" t="n">
-        <v>25.45999908447266</v>
+        <v>57.36000061035156</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6218015737632752</v>
+        <v>0.6499041901334052</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>GENB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13.66B</t>
+          <t>1.97B</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>685.47998046875</v>
+        <v>15.48999977111816</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05</v>
+        <v>7.79</v>
       </c>
       <c r="F25" t="n">
-        <v>685.47998046875</v>
+        <v>15.48999977111816</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6747409728692019</v>
+        <v>0.6650772025431426</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GENB</t>
+          <t>NOEM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.97B</t>
+          <t>100M</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.48999977111816</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="E26" t="n">
-        <v>7.79</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>15.48999977111816</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6650772025431426</v>
+        <v>0.02613695765812859</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GLNG</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5.84B</t>
+          <t>5.37T</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>57.36000061035156</v>
+        <v>220.7799987792969</v>
       </c>
       <c r="E27" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="F27" t="n">
-        <v>57.36000061035156</v>
+        <v>220.7799987792969</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6499041901334052</v>
+        <v>0.9761118533538271</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EHLD</t>
+          <t>LCCC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>24M</t>
+          <t>92M</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8.630000114440918</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="E28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>8.630000114440918</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8241758241758241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DTSQ</t>
+          <t>NESR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>41M</t>
+          <t>2.71B</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.23999977111816</v>
+        <v>26.84000015258789</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02</v>
+        <v>5.54</v>
       </c>
       <c r="F29" t="n">
-        <v>11.23999977111816</v>
+        <v>26.84000015258789</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7252946509519492</v>
+        <v>0.8909203522945157</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DSGN</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2782,61 +2778,61 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>986M</t>
+          <t>15.67B</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.78999996185303</v>
+        <v>155.8000030517578</v>
       </c>
       <c r="E30" t="n">
-        <v>1.15</v>
+        <v>3.46</v>
       </c>
       <c r="F30" t="n">
-        <v>15.78999996185303</v>
+        <v>155.8000030517578</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.187795514631709</v>
+        <v>1.147435268389105</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>NDLS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>357M</t>
+          <t>76M</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.60000038146973</v>
+        <v>12.94999980926514</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="F31" t="n">
-        <v>10.60000038146973</v>
+        <v>12.94999980926514</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.003168648127962686</v>
+        <v>0.8650909165453763</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DMII</t>
+          <t>ORIQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2846,29 +2842,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>639M</t>
+          <t>88M</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.02999973297119</v>
+        <v>10.25</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>10.02999973297119</v>
+        <v>10.25</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.118916230122336</v>
+        <v>0.1855287569573284</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CVGI</t>
+          <t>OLPX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2878,23 +2874,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>182M</t>
+          <t>1.37B</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5.400000095367432</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="E33" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>5.400000095367432</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.004748113805576</v>
+        <v>0.714448430203208</v>
       </c>
     </row>
     <row r="34">
@@ -2964,135 +2960,135 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ASRT</t>
+          <t>DMII</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>146M</t>
+          <t>639M</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>22.54999923706055</v>
+        <v>10.02999973297119</v>
       </c>
       <c r="E36" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>22.54999923706055</v>
+        <v>10.02999973297119</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4156742911068171</v>
+        <v>0.118916230122336</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>DMAA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10.65B</t>
+          <t>357M</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>82.66999816894531</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="E37" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>82.66999816894531</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7662014091676267</v>
+        <v>0.003168648127962686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>EHLD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>309M</t>
+          <t>24M</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.539999961853027</v>
+        <v>8.630000114440918</v>
       </c>
       <c r="E38" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="F38" t="n">
-        <v>5.539999961853027</v>
+        <v>8.630000114440918</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.083318654218778</v>
+        <v>0.8241758241758241</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FSHP</t>
+          <t>CVGI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>55M</t>
+          <t>182M</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.97999954223633</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="E39" t="n">
-        <v>0.09</v>
+        <v>3.65</v>
       </c>
       <c r="F39" t="n">
-        <v>10.97999954223633</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1908396946564886</v>
+        <v>1.004748113805576</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>WTG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3102,61 +3098,61 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5.44B</t>
+          <t>75M</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>87.06999969482422</v>
+        <v>10.30399990081787</v>
       </c>
       <c r="E40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>87.06999969482422</v>
+        <v>10.30399990081787</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9654082846518192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AVR</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>651M</t>
+          <t>4.41B</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6.699999809265137</v>
+        <v>83.91999816894531</v>
       </c>
       <c r="E41" t="n">
-        <v>2.92</v>
+        <v>3.95</v>
       </c>
       <c r="F41" t="n">
-        <v>6.699999809265137</v>
+        <v>83.91999816894531</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6323937556144499</v>
+        <v>1.061656833316082</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WTG</t>
+          <t>DTSQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3166,55 +3162,55 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>75M</t>
+          <t>41M</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.30399990081787</v>
+        <v>11.23999977111816</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F42" t="n">
-        <v>10.30399990081787</v>
+        <v>11.23999977111816</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.7252946509519492</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>DSGN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4.41B</t>
+          <t>986M</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>83.91999816894531</v>
+        <v>15.78999996185303</v>
       </c>
       <c r="E43" t="n">
-        <v>3.95</v>
+        <v>1.15</v>
       </c>
       <c r="F43" t="n">
-        <v>83.91999816894531</v>
+        <v>15.78999996185303</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.061656833316082</v>
+        <v>1.187795514631709</v>
       </c>
     </row>
     <row r="44">
@@ -3444,7 +3440,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TAVI</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3454,23 +3450,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>122M</t>
+          <t>125M</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.60000038146973</v>
+        <v>15.9399995803833</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="F51" t="n">
-        <v>10.61999988555908</v>
+        <v>15.97000026702881</v>
       </c>
       <c r="G51" t="n">
         <v>0.19</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.5975685143210385</v>
       </c>
     </row>
     <row r="52">
@@ -3508,7 +3504,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>DRDB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3518,29 +3514,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>125M</t>
+          <t>323M</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.9399995803833</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="E53" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>15.97000026702881</v>
+        <v>10.53999996185303</v>
       </c>
       <c r="G53" t="n">
         <v>0.19</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5975685143210385</v>
+        <v>0.04183046063904848</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DRDB</t>
+          <t>TAVI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3550,23 +3546,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>323M</t>
+          <t>122M</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.52000045776367</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>10.53999996185303</v>
+        <v>10.61999988555908</v>
       </c>
       <c r="G54" t="n">
         <v>0.19</v>
       </c>
       <c r="H54" t="n">
-        <v>0.04183046063904848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3860,65 +3856,65 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BYFC</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>93M</t>
+          <t>12.43B</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>9.949999809265137</v>
+        <v>49.45999908447266</v>
       </c>
       <c r="E64" t="n">
         <v>-0.5</v>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>49.70999908447266</v>
       </c>
       <c r="G64" t="n">
         <v>0.5</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9393939393939394</v>
+        <v>1.014686326672666</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>BYFC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>12.43B</t>
+          <t>93M</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>49.45999908447266</v>
+        <v>9.949999809265137</v>
       </c>
       <c r="E65" t="n">
         <v>-0.5</v>
       </c>
       <c r="F65" t="n">
-        <v>49.70999908447266</v>
+        <v>10</v>
       </c>
       <c r="G65" t="n">
         <v>0.5</v>
       </c>
       <c r="H65" t="n">
-        <v>1.014686326672666</v>
+        <v>0.9393939393939394</v>
       </c>
     </row>
     <row r="66">
@@ -4116,7 +4112,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ALRS</t>
+          <t>TRST</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4126,29 +4122,29 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>677M</t>
+          <t>852M</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>26.94000053405762</v>
+        <v>48.77000045776367</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.44</v>
+        <v>0.54</v>
       </c>
       <c r="F72" t="n">
-        <v>27.10000038146973</v>
+        <v>49.06000137329102</v>
       </c>
       <c r="G72" t="n">
         <v>0.59</v>
       </c>
       <c r="H72" t="n">
-        <v>1.121073281196514</v>
+        <v>1.033580462276494</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TRST</t>
+          <t>ALRS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4158,23 +4154,23 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>852M</t>
+          <t>677M</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>48.77000045776367</v>
+        <v>26.94000053405762</v>
       </c>
       <c r="E73" t="n">
-        <v>0.54</v>
+        <v>-0.44</v>
       </c>
       <c r="F73" t="n">
-        <v>49.06000137329102</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="G73" t="n">
         <v>0.59</v>
       </c>
       <c r="H73" t="n">
-        <v>1.033580462276494</v>
+        <v>1.121073281196514</v>
       </c>
     </row>
     <row r="74">
@@ -4464,65 +4460,65 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>TFSL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>204.87B</t>
+          <t>4.20B</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>419.6499938964844</v>
+        <v>14.98999977111816</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>422.7300109863281</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="G83" t="n">
         <v>0.73</v>
       </c>
       <c r="H83" t="n">
-        <v>1.360993991378715</v>
+        <v>2.566824737027233</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TFSL</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4.20B</t>
+          <t>204.87B</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>14.98999977111816</v>
+        <v>419.6499938964844</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.73</v>
       </c>
       <c r="F84" t="n">
-        <v>15.10000038146973</v>
+        <v>422.7300109863281</v>
       </c>
       <c r="G84" t="n">
         <v>0.73</v>
       </c>
       <c r="H84" t="n">
-        <v>2.566824737027233</v>
+        <v>1.360993991378715</v>
       </c>
     </row>
     <row r="85">
@@ -4560,129 +4556,129 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SLAB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>572M</t>
+          <t>7.14B</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.55000019073486</v>
+        <v>216.5800018310547</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.77</v>
+        <v>-0.29</v>
       </c>
       <c r="F86" t="n">
-        <v>11.64000034332275</v>
+        <v>218.2700042724609</v>
       </c>
       <c r="G86" t="n">
         <v>0.77</v>
       </c>
       <c r="H86" t="n">
-        <v>1.117958181608476</v>
+        <v>0.7822251990901222</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>7.14B</t>
+          <t>572M</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>216.5800018310547</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.29</v>
+        <v>-0.77</v>
       </c>
       <c r="F87" t="n">
-        <v>218.2700042724609</v>
+        <v>11.64000034332275</v>
       </c>
       <c r="G87" t="n">
         <v>0.77</v>
       </c>
       <c r="H87" t="n">
-        <v>0.7822251990901222</v>
+        <v>1.117958181608476</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TTMI</t>
+          <t>GASS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>16.96B</t>
+          <t>381M</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>163.3600006103516</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="E88" t="n">
-        <v>0.23</v>
+        <v>1.79</v>
       </c>
       <c r="F88" t="n">
-        <v>164.6399993896484</v>
+        <v>10.31999969482422</v>
       </c>
       <c r="G88" t="n">
         <v>0.78</v>
       </c>
       <c r="H88" t="n">
-        <v>1.027740310231285</v>
+        <v>0.7900398546890982</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GASS</t>
+          <t>TTMI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>381M</t>
+          <t>16.96B</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.23999977111816</v>
+        <v>163.3600006103516</v>
       </c>
       <c r="E89" t="n">
-        <v>1.79</v>
+        <v>0.23</v>
       </c>
       <c r="F89" t="n">
-        <v>10.31999969482422</v>
+        <v>164.6399993896484</v>
       </c>
       <c r="G89" t="n">
         <v>0.78</v>
       </c>
       <c r="H89" t="n">
-        <v>0.7900398546890982</v>
+        <v>1.027740310231285</v>
       </c>
     </row>
     <row r="90">
@@ -5104,65 +5100,65 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>ELVR</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>11.10B</t>
+          <t>1.77B</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>92.29000091552734</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="E103" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>93.22515106201172</v>
+        <v>98.80000305175781</v>
       </c>
       <c r="G103" t="n">
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>1.000396538926905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ELVR</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1.77B</t>
+          <t>11.10B</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>97.80999755859375</v>
+        <v>92.29000091552734</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="F104" t="n">
-        <v>98.80000305175781</v>
+        <v>93.22515106201172</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1.000396538926905</v>
       </c>
     </row>
     <row r="105">
@@ -5512,7 +5508,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MYFW</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5522,29 +5518,29 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>283M</t>
+          <t>106M</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>29.05999946594238</v>
+        <v>17</v>
       </c>
       <c r="E116" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="F116" t="n">
-        <v>29.39999961853027</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="G116" t="n">
         <v>1.16</v>
       </c>
       <c r="H116" t="n">
-        <v>1.629425919559986</v>
+        <v>0.2221235006663705</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>MYFW</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5554,23 +5550,23 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>106M</t>
+          <t>283M</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>17</v>
+        <v>29.05999946594238</v>
       </c>
       <c r="E117" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="F117" t="n">
-        <v>17.20000076293945</v>
+        <v>29.39999961853027</v>
       </c>
       <c r="G117" t="n">
         <v>1.16</v>
       </c>
       <c r="H117" t="n">
-        <v>0.2221235006663705</v>
+        <v>1.629425919559986</v>
       </c>
     </row>
     <row r="118">
@@ -6276,97 +6272,97 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>LYTS</t>
+          <t>CADL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>888M</t>
+          <t>639M</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>24.20000076293945</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.53</v>
+        <v>-1.47</v>
       </c>
       <c r="F140" t="n">
-        <v>24.55999946594238</v>
+        <v>8.850000381469727</v>
       </c>
       <c r="G140" t="n">
         <v>1.47</v>
       </c>
       <c r="H140" t="n">
-        <v>1.316556882118842</v>
+        <v>1.710865490240774</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>LYTS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>18.85B</t>
+          <t>888M</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>127.629997253418</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.34</v>
+        <v>-0.53</v>
       </c>
       <c r="F141" t="n">
-        <v>129.5299987792969</v>
+        <v>24.55999946594238</v>
       </c>
       <c r="G141" t="n">
         <v>1.47</v>
       </c>
       <c r="H141" t="n">
-        <v>0.768932831078011</v>
+        <v>1.316556882118842</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CADL</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>639M</t>
+          <t>18.85B</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>8.720000267028809</v>
+        <v>127.629997253418</v>
       </c>
       <c r="E142" t="n">
-        <v>-1.47</v>
+        <v>-0.34</v>
       </c>
       <c r="F142" t="n">
-        <v>8.850000381469727</v>
+        <v>129.5299987792969</v>
       </c>
       <c r="G142" t="n">
         <v>1.47</v>
       </c>
       <c r="H142" t="n">
-        <v>1.710865490240774</v>
+        <v>0.768932831078011</v>
       </c>
     </row>
     <row r="143">
@@ -6916,193 +6912,193 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>USEA</t>
+          <t>TBLA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>22M</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2.299999952316284</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="E160" t="n">
-        <v>1.32</v>
+        <v>0.58</v>
       </c>
       <c r="F160" t="n">
-        <v>2.339999914169312</v>
+        <v>5.25</v>
       </c>
       <c r="G160" t="n">
         <v>1.71</v>
       </c>
       <c r="H160" t="n">
-        <v>0.3740279310066464</v>
+        <v>1.268080474769054</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NPAC</t>
+          <t>USEA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>396M</t>
+          <t>22M</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>10.31999969482422</v>
+        <v>2.299999952316284</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.39</v>
+        <v>1.32</v>
       </c>
       <c r="F161" t="n">
-        <v>10.5</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="G161" t="n">
         <v>1.71</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1560245875933011</v>
+        <v>0.3740279310066464</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TBLA</t>
+          <t>NPAC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>396M</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>5.159999847412109</v>
+        <v>10.31999969482422</v>
       </c>
       <c r="E162" t="n">
-        <v>0.58</v>
+        <v>-0.39</v>
       </c>
       <c r="F162" t="n">
-        <v>5.25</v>
+        <v>10.5</v>
       </c>
       <c r="G162" t="n">
         <v>1.71</v>
       </c>
       <c r="H162" t="n">
-        <v>1.268080474769054</v>
+        <v>0.1560245875933011</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5.50B</t>
+          <t>5.02B</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>39.65000152587891</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.15</v>
+        <v>-1.73</v>
       </c>
       <c r="F163" t="n">
-        <v>40.34999847412109</v>
+        <v>24.28000068664551</v>
       </c>
       <c r="G163" t="n">
         <v>1.73</v>
       </c>
       <c r="H163" t="n">
-        <v>0.8538866803306876</v>
+        <v>1.904912231368565</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MATW</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>867M</t>
+          <t>5.50B</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>27.86000061035156</v>
+        <v>39.65000152587891</v>
       </c>
       <c r="E164" t="n">
-        <v>0.32</v>
+        <v>-0.15</v>
       </c>
       <c r="F164" t="n">
-        <v>28.35074234008789</v>
+        <v>40.34999847412109</v>
       </c>
       <c r="G164" t="n">
         <v>1.73</v>
       </c>
       <c r="H164" t="n">
-        <v>1.377459386510538</v>
+        <v>0.8538866803306876</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>MATW</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>5.02B</t>
+          <t>867M</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>23.86000061035156</v>
+        <v>27.86000061035156</v>
       </c>
       <c r="E165" t="n">
-        <v>-1.73</v>
+        <v>0.32</v>
       </c>
       <c r="F165" t="n">
-        <v>24.28000068664551</v>
+        <v>28.35074234008789</v>
       </c>
       <c r="G165" t="n">
         <v>1.73</v>
       </c>
       <c r="H165" t="n">
-        <v>1.904912231368565</v>
+        <v>1.377459386510538</v>
       </c>
     </row>
     <row r="166">
@@ -7268,7 +7264,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>BAYA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7278,87 +7274,87 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>488M</t>
+          <t>33M</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>37.29000091552734</v>
+        <v>11.88000011444092</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.67</v>
+        <v>0.76</v>
       </c>
       <c r="F171" t="n">
-        <v>37.97999954223633</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="G171" t="n">
         <v>1.82</v>
       </c>
       <c r="H171" t="n">
-        <v>1.799163179916318</v>
+        <v>2.235099337748344</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SYRE</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>6.52B</t>
+          <t>488M</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>75.04000091552734</v>
+        <v>37.29000091552734</v>
       </c>
       <c r="E172" t="n">
-        <v>-1.82</v>
+        <v>-0.67</v>
       </c>
       <c r="F172" t="n">
-        <v>76.43000030517578</v>
+        <v>37.97999954223633</v>
       </c>
       <c r="G172" t="n">
         <v>1.82</v>
       </c>
       <c r="H172" t="n">
-        <v>1.532317591186998</v>
+        <v>1.799163179916318</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BAYA</t>
+          <t>SYRE</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>33M</t>
+          <t>6.52B</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.88000011444092</v>
+        <v>75.04000091552734</v>
       </c>
       <c r="E173" t="n">
-        <v>0.76</v>
+        <v>-1.82</v>
       </c>
       <c r="F173" t="n">
-        <v>12.10000038146973</v>
+        <v>76.43000030517578</v>
       </c>
       <c r="G173" t="n">
         <v>1.82</v>
       </c>
       <c r="H173" t="n">
-        <v>2.235099337748344</v>
+        <v>1.532317591186998</v>
       </c>
     </row>
     <row r="174">
@@ -7396,65 +7392,65 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CGON</t>
+          <t>LARK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>6.36B</t>
+          <t>171M</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>72.06999969482422</v>
+        <v>28.05999946594238</v>
       </c>
       <c r="E175" t="n">
-        <v>3.97</v>
+        <v>0.72</v>
       </c>
       <c r="F175" t="n">
-        <v>73.43000030517578</v>
+        <v>28.58983612060547</v>
       </c>
       <c r="G175" t="n">
         <v>1.85</v>
       </c>
       <c r="H175" t="n">
-        <v>1.269806463767355</v>
+        <v>0.3119682359614294</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>LARK</t>
+          <t>CGON</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>171M</t>
+          <t>6.36B</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>28.05999946594238</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="E176" t="n">
-        <v>0.72</v>
+        <v>3.97</v>
       </c>
       <c r="F176" t="n">
-        <v>28.58983612060547</v>
+        <v>73.43000030517578</v>
       </c>
       <c r="G176" t="n">
         <v>1.85</v>
       </c>
       <c r="H176" t="n">
-        <v>0.3119682359614294</v>
+        <v>1.269806463767355</v>
       </c>
     </row>
     <row r="177">
@@ -7556,65 +7552,65 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CPBI</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>74M</t>
+          <t>6.73B</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>17.51000022888184</v>
+        <v>82.11000061035156</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="F180" t="n">
-        <v>17.85000038146973</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="G180" t="n">
         <v>1.9</v>
       </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>0.9622037980364355</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>CPBI</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>6.73B</t>
+          <t>74M</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>82.11000061035156</v>
+        <v>17.51000022888184</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.91</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>83.69999694824219</v>
+        <v>17.85000038146973</v>
       </c>
       <c r="G181" t="n">
         <v>1.9</v>
       </c>
       <c r="H181" t="n">
-        <v>0.9622037980364355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -7876,12 +7872,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RBKB</t>
+          <t>RFIL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7890,30 +7886,30 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>16.14999961853027</v>
+        <v>16.60000038146973</v>
       </c>
       <c r="E190" t="n">
-        <v>0.5600000000000001</v>
+        <v>-2.06</v>
       </c>
       <c r="F190" t="n">
-        <v>16.48999977111816</v>
+        <v>16.95000076293945</v>
       </c>
       <c r="G190" t="n">
         <v>2.06</v>
       </c>
       <c r="H190" t="n">
-        <v>6.514266070814713</v>
+        <v>1.304097909132278</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RFIL</t>
+          <t>RBKB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7922,19 +7918,19 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>16.60000038146973</v>
+        <v>16.14999961853027</v>
       </c>
       <c r="E191" t="n">
-        <v>-2.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F191" t="n">
-        <v>16.95000076293945</v>
+        <v>16.48999977111816</v>
       </c>
       <c r="G191" t="n">
         <v>2.06</v>
       </c>
       <c r="H191" t="n">
-        <v>1.304097909132278</v>
+        <v>6.514266070814713</v>
       </c>
     </row>
     <row r="192">
@@ -7972,65 +7968,65 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TRIN</t>
+          <t>AYA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>1.52B</t>
+          <t>3.03B</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>16.92000007629395</v>
+        <v>21.18000030517578</v>
       </c>
       <c r="E193" t="n">
-        <v>0.77</v>
+        <v>6.65</v>
       </c>
       <c r="F193" t="n">
-        <v>17.28000068664551</v>
+        <v>21.6299991607666</v>
       </c>
       <c r="G193" t="n">
         <v>2.08</v>
       </c>
       <c r="H193" t="n">
-        <v>0.7041440883195387</v>
+        <v>1.594021499042851</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>AYA</t>
+          <t>TRIN</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>3.03B</t>
+          <t>1.52B</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>21.18000030517578</v>
+        <v>16.92000007629395</v>
       </c>
       <c r="E194" t="n">
-        <v>6.65</v>
+        <v>0.77</v>
       </c>
       <c r="F194" t="n">
-        <v>21.6299991607666</v>
+        <v>17.28000068664551</v>
       </c>
       <c r="G194" t="n">
         <v>2.08</v>
       </c>
       <c r="H194" t="n">
-        <v>1.594021499042851</v>
+        <v>0.7041440883195387</v>
       </c>
     </row>
     <row r="195">
@@ -8100,65 +8096,65 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AIP</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.49B</t>
+          <t>790M</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>32.43000030517578</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="E197" t="n">
-        <v>-2.11</v>
+        <v>-0.36</v>
       </c>
       <c r="F197" t="n">
-        <v>33.13000106811523</v>
+        <v>67.84999847412109</v>
       </c>
       <c r="G197" t="n">
         <v>2.11</v>
       </c>
       <c r="H197" t="n">
-        <v>2.103371612924795</v>
+        <v>0.8064908524717789</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>AIP</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>790M</t>
+          <t>1.49B</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>66.41999816894531</v>
+        <v>32.43000030517578</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.36</v>
+        <v>-2.11</v>
       </c>
       <c r="F198" t="n">
-        <v>67.84999847412109</v>
+        <v>33.13000106811523</v>
       </c>
       <c r="G198" t="n">
         <v>2.11</v>
       </c>
       <c r="H198" t="n">
-        <v>0.8064908524717789</v>
+        <v>2.103371612924795</v>
       </c>
     </row>
     <row r="199">
@@ -8516,65 +8512,65 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>730.98B</t>
+          <t>15.10B</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>448.2900085449219</v>
+        <v>21.76000022888184</v>
       </c>
       <c r="E210" t="n">
-        <v>-2.29</v>
+        <v>-0.09</v>
       </c>
       <c r="F210" t="n">
-        <v>458.7900085449219</v>
+        <v>22.27000045776367</v>
       </c>
       <c r="G210" t="n">
         <v>2.29</v>
       </c>
       <c r="H210" t="n">
-        <v>0.9878241191363237</v>
+        <v>1.007383709291643</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>15.10B</t>
+          <t>730.98B</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>21.76000022888184</v>
+        <v>448.2900085449219</v>
       </c>
       <c r="E211" t="n">
-        <v>-0.09</v>
+        <v>-2.29</v>
       </c>
       <c r="F211" t="n">
-        <v>22.27000045776367</v>
+        <v>458.7900085449219</v>
       </c>
       <c r="G211" t="n">
         <v>2.29</v>
       </c>
       <c r="H211" t="n">
-        <v>1.007383709291643</v>
+        <v>0.9878241191363237</v>
       </c>
     </row>
     <row r="212">
@@ -8612,129 +8608,129 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CNOB</t>
+          <t>OSS</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>1.48B</t>
+          <t>385M</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>29.45999908447266</v>
+        <v>15.55000019073486</v>
       </c>
       <c r="E213" t="n">
-        <v>-0.91</v>
+        <v>-2.32</v>
       </c>
       <c r="F213" t="n">
-        <v>30.15999984741211</v>
+        <v>15.92000007629395</v>
       </c>
       <c r="G213" t="n">
         <v>2.32</v>
       </c>
       <c r="H213" t="n">
-        <v>0.7519399553423386</v>
+        <v>1.372639395549008</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>OSS</t>
+          <t>CNOB</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>385M</t>
+          <t>1.48B</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>15.55000019073486</v>
+        <v>29.45999908447266</v>
       </c>
       <c r="E214" t="n">
-        <v>-2.32</v>
+        <v>-0.91</v>
       </c>
       <c r="F214" t="n">
-        <v>15.92000007629395</v>
+        <v>30.15999984741211</v>
       </c>
       <c r="G214" t="n">
         <v>2.32</v>
       </c>
       <c r="H214" t="n">
-        <v>1.372639395549008</v>
+        <v>0.7519399553423386</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>WFRD</t>
+          <t>TUSK</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>7.73B</t>
+          <t>142M</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>107.5100021362305</v>
+        <v>2.940000057220459</v>
       </c>
       <c r="E215" t="n">
-        <v>5.11</v>
+        <v>1.03</v>
       </c>
       <c r="F215" t="n">
-        <v>110.0705947875977</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="G215" t="n">
         <v>2.33</v>
       </c>
       <c r="H215" t="n">
-        <v>1.064475140386113</v>
+        <v>1.298923694575345</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TUSK</t>
+          <t>WFRD</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>142M</t>
+          <t>7.73B</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2.940000057220459</v>
+        <v>107.5100021362305</v>
       </c>
       <c r="E216" t="n">
-        <v>1.03</v>
+        <v>5.11</v>
       </c>
       <c r="F216" t="n">
-        <v>3.009999990463257</v>
+        <v>110.0705947875977</v>
       </c>
       <c r="G216" t="n">
         <v>2.33</v>
       </c>
       <c r="H216" t="n">
-        <v>1.298923694575345</v>
+        <v>1.064475140386113</v>
       </c>
     </row>
     <row r="217">
@@ -9124,65 +9120,65 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>WSBF</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>174.85B</t>
+          <t>330M</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>215.6000061035156</v>
+        <v>18.27000045776367</v>
       </c>
       <c r="E229" t="n">
-        <v>0.91</v>
+        <v>-0.38</v>
       </c>
       <c r="F229" t="n">
-        <v>221.3800048828125</v>
+        <v>18.76000022888184</v>
       </c>
       <c r="G229" t="n">
         <v>2.61</v>
       </c>
       <c r="H229" t="n">
-        <v>1.072086356076442</v>
+        <v>0.9960491903622503</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>WSBF</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>330M</t>
+          <t>174.85B</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>18.27000045776367</v>
+        <v>215.6000061035156</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.38</v>
+        <v>0.91</v>
       </c>
       <c r="F230" t="n">
-        <v>18.76000022888184</v>
+        <v>221.3800048828125</v>
       </c>
       <c r="G230" t="n">
         <v>2.61</v>
       </c>
       <c r="H230" t="n">
-        <v>0.9960491903622503</v>
+        <v>1.072086356076442</v>
       </c>
     </row>
     <row r="231">
@@ -9412,7 +9408,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PGC</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -9422,29 +9418,29 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>744M</t>
+          <t>904M</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>41.97000122070312</v>
+        <v>30.5</v>
       </c>
       <c r="E238" t="n">
-        <v>-0.14</v>
+        <v>-0.75</v>
       </c>
       <c r="F238" t="n">
-        <v>43.13999938964844</v>
+        <v>31.35000038146973</v>
       </c>
       <c r="G238" t="n">
         <v>2.71</v>
       </c>
       <c r="H238" t="n">
-        <v>0.6727561556791104</v>
+        <v>0.5743047889397046</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>PGC</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -9454,23 +9450,23 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>904M</t>
+          <t>744M</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>30.5</v>
+        <v>41.97000122070312</v>
       </c>
       <c r="E239" t="n">
-        <v>-0.75</v>
+        <v>-0.14</v>
       </c>
       <c r="F239" t="n">
-        <v>31.35000038146973</v>
+        <v>43.13999938964844</v>
       </c>
       <c r="G239" t="n">
         <v>2.71</v>
       </c>
       <c r="H239" t="n">
-        <v>0.5743047889397046</v>
+        <v>0.6727561556791104</v>
       </c>
     </row>
     <row r="240">
@@ -9652,7 +9648,7 @@
         <v>2.24</v>
       </c>
       <c r="F245" t="n">
-        <v>1050.93408203125</v>
+        <v>1050.933959960938</v>
       </c>
       <c r="G245" t="n">
         <v>2.76</v>
@@ -9952,65 +9948,65 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>IMVT</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>5.83B</t>
+          <t>9.64B</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>28.64999961853027</v>
+        <v>70.98999786376953</v>
       </c>
       <c r="E255" t="n">
-        <v>-1.41</v>
+        <v>-2.85</v>
       </c>
       <c r="F255" t="n">
-        <v>29.48999977111816</v>
+        <v>73.06999969482422</v>
       </c>
       <c r="G255" t="n">
         <v>2.85</v>
       </c>
       <c r="H255" t="n">
-        <v>0.8115337061129924</v>
+        <v>0.8649254883216076</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>IMVT</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>9.64B</t>
+          <t>5.83B</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>70.98999786376953</v>
+        <v>28.64999961853027</v>
       </c>
       <c r="E256" t="n">
-        <v>-2.85</v>
+        <v>-1.41</v>
       </c>
       <c r="F256" t="n">
-        <v>73.06999969482422</v>
+        <v>29.48999977111816</v>
       </c>
       <c r="G256" t="n">
         <v>2.85</v>
       </c>
       <c r="H256" t="n">
-        <v>0.8649254883216076</v>
+        <v>0.8115337061129924</v>
       </c>
     </row>
     <row r="257">
@@ -10528,65 +10524,65 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TSAT</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2.73B</t>
+          <t>71.79B</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>53.20999908447266</v>
+        <v>131.9400024414062</v>
       </c>
       <c r="E273" t="n">
-        <v>-3.1</v>
+        <v>0.95</v>
       </c>
       <c r="F273" t="n">
-        <v>54.90999984741211</v>
+        <v>136.1611328125</v>
       </c>
       <c r="G273" t="n">
         <v>3.1</v>
       </c>
       <c r="H273" t="n">
-        <v>0.8952445087048664</v>
+        <v>0.8534158044377249</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>TSAT</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>71.79B</t>
+          <t>2.73B</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>131.9400024414062</v>
+        <v>53.20999908447266</v>
       </c>
       <c r="E274" t="n">
-        <v>0.95</v>
+        <v>-3.1</v>
       </c>
       <c r="F274" t="n">
-        <v>136.1611328125</v>
+        <v>54.90999984741211</v>
       </c>
       <c r="G274" t="n">
         <v>3.1</v>
       </c>
       <c r="H274" t="n">
-        <v>0.8534158044377249</v>
+        <v>0.8952445087048664</v>
       </c>
     </row>
     <row r="275">
@@ -10624,7 +10620,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>FFBC</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -10634,29 +10630,29 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>3.14B</t>
+          <t>2.07B</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>29.92000007629395</v>
+        <v>33.56999969482422</v>
       </c>
       <c r="E276" t="n">
-        <v>-0.63</v>
+        <v>-3.12</v>
       </c>
       <c r="F276" t="n">
-        <v>30.88247871398926</v>
+        <v>34.65000152587891</v>
       </c>
       <c r="G276" t="n">
         <v>3.12</v>
       </c>
       <c r="H276" t="n">
-        <v>0.859236910382181</v>
+        <v>1.180382635317359</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>FFBC</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -10666,29 +10662,29 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>5.97B</t>
+          <t>3.14B</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>42.79999923706055</v>
+        <v>29.92000007629395</v>
       </c>
       <c r="E277" t="n">
-        <v>-0.14</v>
+        <v>-0.63</v>
       </c>
       <c r="F277" t="n">
-        <v>44.18000030517578</v>
+        <v>30.88247871398926</v>
       </c>
       <c r="G277" t="n">
         <v>3.12</v>
       </c>
       <c r="H277" t="n">
-        <v>1.040995515128545</v>
+        <v>0.859236910382181</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -10698,23 +10694,23 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2.07B</t>
+          <t>5.97B</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>33.56999969482422</v>
+        <v>42.79999923706055</v>
       </c>
       <c r="E278" t="n">
-        <v>-3.12</v>
+        <v>-0.14</v>
       </c>
       <c r="F278" t="n">
-        <v>34.65000152587891</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="G278" t="n">
         <v>3.12</v>
       </c>
       <c r="H278" t="n">
-        <v>1.180382635317359</v>
+        <v>1.040995515128545</v>
       </c>
     </row>
     <row r="279">
@@ -11040,7 +11036,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>EFSC</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -11050,23 +11046,23 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2.16B</t>
+          <t>389M</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>59.06999969482422</v>
+        <v>10.35999965667725</v>
       </c>
       <c r="E289" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="F289" t="n">
-        <v>61.06383514404297</v>
+        <v>10.71000003814697</v>
       </c>
       <c r="G289" t="n">
         <v>3.27</v>
       </c>
       <c r="H289" t="n">
-        <v>0.8710070100323217</v>
+        <v>0.7288035851704314</v>
       </c>
     </row>
     <row r="290">
@@ -11104,7 +11100,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>EFSC</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -11114,23 +11110,23 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>389M</t>
+          <t>2.16B</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>10.35999965667725</v>
+        <v>59.06999969482422</v>
       </c>
       <c r="E291" t="n">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="F291" t="n">
-        <v>10.71000003814697</v>
+        <v>61.06383514404297</v>
       </c>
       <c r="G291" t="n">
         <v>3.27</v>
       </c>
       <c r="H291" t="n">
-        <v>0.7288035851704314</v>
+        <v>0.8710070100323217</v>
       </c>
     </row>
     <row r="292">
@@ -11264,12 +11260,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11278,30 +11274,30 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>81.61000061035156</v>
+        <v>17.47999954223633</v>
       </c>
       <c r="E296" t="n">
-        <v>-0.87</v>
+        <v>-3.32</v>
       </c>
       <c r="F296" t="n">
-        <v>84.41000366210938</v>
+        <v>18.07999992370605</v>
       </c>
       <c r="G296" t="n">
         <v>3.32</v>
       </c>
       <c r="H296" t="n">
-        <v>1.116187645885374</v>
+        <v>0.9315478012928307</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11310,115 +11306,115 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>17.47999954223633</v>
+        <v>81.61000061035156</v>
       </c>
       <c r="E297" t="n">
-        <v>-3.32</v>
+        <v>-0.87</v>
       </c>
       <c r="F297" t="n">
-        <v>18.07999992370605</v>
+        <v>84.41000366210938</v>
       </c>
       <c r="G297" t="n">
         <v>3.32</v>
       </c>
       <c r="H297" t="n">
-        <v>0.9315478012928307</v>
+        <v>1.116187645885374</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2.86T</t>
+          <t>268M</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>265.8200073242188</v>
+        <v>18.59000015258789</v>
       </c>
       <c r="E298" t="n">
-        <v>-1.18</v>
+        <v>0.49</v>
       </c>
       <c r="F298" t="n">
-        <v>274.989990234375</v>
+        <v>19.22999954223633</v>
       </c>
       <c r="G298" t="n">
         <v>3.33</v>
       </c>
       <c r="H298" t="n">
-        <v>0.7896862415182426</v>
+        <v>0.7257708809495168</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>4.65T</t>
+          <t>2.86T</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>383.8200073242188</v>
+        <v>265.8200073242188</v>
       </c>
       <c r="E299" t="n">
-        <v>-0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="F299" t="n">
-        <v>397.0499877929688</v>
+        <v>274.989990234375</v>
       </c>
       <c r="G299" t="n">
         <v>3.33</v>
       </c>
       <c r="H299" t="n">
-        <v>0.8982965602049711</v>
+        <v>0.7896862415182426</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>268M</t>
+          <t>4.65T</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>18.59000015258789</v>
+        <v>383.8200073242188</v>
       </c>
       <c r="E300" t="n">
-        <v>0.49</v>
+        <v>-0.76</v>
       </c>
       <c r="F300" t="n">
-        <v>19.22999954223633</v>
+        <v>397.0499877929688</v>
       </c>
       <c r="G300" t="n">
         <v>3.33</v>
       </c>
       <c r="H300" t="n">
-        <v>0.7257708809495168</v>
+        <v>0.8982965602049711</v>
       </c>
     </row>
     <row r="301">
@@ -11744,7 +11740,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>SHAZ</t>
+          <t>TSEM</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -11754,55 +11750,55 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>848M</t>
+          <t>26.28B</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>52.09999847412109</v>
+        <v>220.8300018310547</v>
       </c>
       <c r="E311" t="n">
-        <v>-3.18</v>
+        <v>-3.52</v>
       </c>
       <c r="F311" t="n">
-        <v>54</v>
+        <v>228.8800048828125</v>
       </c>
       <c r="G311" t="n">
         <v>3.52</v>
       </c>
       <c r="H311" t="n">
-        <v>0.7840024508779992</v>
+        <v>0.7731002666023749</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>TSEM</t>
+          <t>QETA</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>26.28B</t>
+          <t>43M</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>220.8300018310547</v>
+        <v>11.5</v>
       </c>
       <c r="E312" t="n">
-        <v>-3.52</v>
+        <v>0</v>
       </c>
       <c r="F312" t="n">
-        <v>228.8800048828125</v>
+        <v>11.92000007629395</v>
       </c>
       <c r="G312" t="n">
         <v>3.52</v>
       </c>
       <c r="H312" t="n">
-        <v>0.7731002666023749</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -11840,33 +11836,33 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>QETA</t>
+          <t>SHAZ</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>43M</t>
+          <t>848M</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>11.5</v>
+        <v>52.09999847412109</v>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>-3.18</v>
       </c>
       <c r="F314" t="n">
-        <v>11.92000007629395</v>
+        <v>54</v>
       </c>
       <c r="G314" t="n">
         <v>3.52</v>
       </c>
       <c r="H314" t="n">
-        <v>0</v>
+        <v>0.7840024508779992</v>
       </c>
     </row>
     <row r="315">
@@ -12384,39 +12380,39 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>TRMK</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.57B</t>
+          <t>33.57B</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>43.79999923706055</v>
+        <v>232.8000030517578</v>
       </c>
       <c r="E331" t="n">
-        <v>-0.68</v>
+        <v>-1.34</v>
       </c>
       <c r="F331" t="n">
-        <v>45.5</v>
+        <v>241.8500061035156</v>
       </c>
       <c r="G331" t="n">
         <v>3.74</v>
       </c>
       <c r="H331" t="n">
-        <v>0.8541569132334582</v>
+        <v>0.8197284579690525</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>CBK</t>
+          <t>TRMK</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -12426,119 +12422,119 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>391M</t>
+          <t>2.57B</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>28.54000091552734</v>
+        <v>43.79999923706055</v>
       </c>
       <c r="E332" t="n">
-        <v>-1.48</v>
+        <v>-0.68</v>
       </c>
       <c r="F332" t="n">
-        <v>29.64999961853027</v>
+        <v>45.5</v>
       </c>
       <c r="G332" t="n">
         <v>3.74</v>
       </c>
       <c r="H332" t="n">
-        <v>0.7487902552978475</v>
+        <v>0.8541569132334582</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>CBK</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>33.57B</t>
+          <t>391M</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>232.8000030517578</v>
+        <v>28.54000091552734</v>
       </c>
       <c r="E333" t="n">
-        <v>-1.34</v>
+        <v>-1.48</v>
       </c>
       <c r="F333" t="n">
-        <v>241.8500061035156</v>
+        <v>29.64999961853027</v>
       </c>
       <c r="G333" t="n">
         <v>3.74</v>
       </c>
       <c r="H333" t="n">
-        <v>0.8197284579690525</v>
+        <v>0.7487902552978475</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>STRZ</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>16.56B</t>
+          <t>342M</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>120.9100036621094</v>
+        <v>20.35000038146973</v>
       </c>
       <c r="E334" t="n">
-        <v>-0.82</v>
+        <v>-3.78</v>
       </c>
       <c r="F334" t="n">
-        <v>125.6658706665039</v>
+        <v>21.14999961853027</v>
       </c>
       <c r="G334" t="n">
         <v>3.78</v>
       </c>
       <c r="H334" t="n">
-        <v>0.925573509567143</v>
+        <v>0.7835929186417723</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>STRZ</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>342M</t>
+          <t>16.56B</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>20.35000038146973</v>
+        <v>120.9100036621094</v>
       </c>
       <c r="E335" t="n">
-        <v>-3.78</v>
+        <v>-0.82</v>
       </c>
       <c r="F335" t="n">
-        <v>21.14999961853027</v>
+        <v>125.6658706665039</v>
       </c>
       <c r="G335" t="n">
         <v>3.78</v>
       </c>
       <c r="H335" t="n">
-        <v>0.7835929186417723</v>
+        <v>0.925573509567143</v>
       </c>
     </row>
     <row r="336">
@@ -12800,65 +12796,65 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>FVCB</t>
+          <t>PKOH</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>279M</t>
+          <t>427M</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>15.48999977111816</v>
+        <v>29.63999938964844</v>
       </c>
       <c r="E344" t="n">
-        <v>-0.64</v>
+        <v>-3.67</v>
       </c>
       <c r="F344" t="n">
-        <v>16.11776924133301</v>
+        <v>30.84000015258789</v>
       </c>
       <c r="G344" t="n">
         <v>3.89</v>
       </c>
       <c r="H344" t="n">
-        <v>1.028776271852288</v>
+        <v>1.685415669379288</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>FVCB</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>427M</t>
+          <t>279M</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>29.63999938964844</v>
+        <v>15.48999977111816</v>
       </c>
       <c r="E345" t="n">
-        <v>-3.67</v>
+        <v>-0.64</v>
       </c>
       <c r="F345" t="n">
-        <v>30.84000015258789</v>
+        <v>16.11776924133301</v>
       </c>
       <c r="G345" t="n">
         <v>3.89</v>
       </c>
       <c r="H345" t="n">
-        <v>1.685415669379288</v>
+        <v>1.028776271852288</v>
       </c>
     </row>
     <row r="346">
@@ -13120,71 +13116,71 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>1.52B</t>
+          <t>49.88B</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>22.1200008392334</v>
+        <v>79.90000152587891</v>
       </c>
       <c r="E354" t="n">
-        <v>-1.03</v>
+        <v>-0.87</v>
       </c>
       <c r="F354" t="n">
-        <v>23.05999946594238</v>
+        <v>83.29433441162109</v>
       </c>
       <c r="G354" t="n">
         <v>4.08</v>
       </c>
       <c r="H354" t="n">
-        <v>0.5804572822793278</v>
+        <v>2.01506173225116</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>49.88B</t>
+          <t>1.52B</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>79.90000152587891</v>
+        <v>22.1200008392334</v>
       </c>
       <c r="E355" t="n">
-        <v>-0.87</v>
+        <v>-1.03</v>
       </c>
       <c r="F355" t="n">
-        <v>83.29433441162109</v>
+        <v>23.05999946594238</v>
       </c>
       <c r="G355" t="n">
         <v>4.08</v>
       </c>
       <c r="H355" t="n">
-        <v>2.01506173225116</v>
+        <v>0.5804572822793278</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>MCBS</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -13194,29 +13190,29 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>252M</t>
+          <t>899M</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>56.09999847412109</v>
+        <v>31.3799991607666</v>
       </c>
       <c r="E356" t="n">
-        <v>0.25</v>
+        <v>-1.2</v>
       </c>
       <c r="F356" t="n">
-        <v>58.5</v>
+        <v>32.72000122070312</v>
       </c>
       <c r="G356" t="n">
         <v>4.1</v>
       </c>
       <c r="H356" t="n">
-        <v>0.5547979171832382</v>
+        <v>0.652251107331751</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>MCBS</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -13226,23 +13222,23 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>899M</t>
+          <t>252M</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>31.3799991607666</v>
+        <v>56.09999847412109</v>
       </c>
       <c r="E357" t="n">
-        <v>-1.2</v>
+        <v>0.25</v>
       </c>
       <c r="F357" t="n">
-        <v>32.72000122070312</v>
+        <v>58.5</v>
       </c>
       <c r="G357" t="n">
         <v>4.1</v>
       </c>
       <c r="H357" t="n">
-        <v>0.652251107331751</v>
+        <v>0.5547979171832382</v>
       </c>
     </row>
     <row r="358">
@@ -13568,65 +13564,65 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>TRS</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>22.04B</t>
+          <t>1.47B</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>102.8399963378906</v>
+        <v>40.90000152587891</v>
       </c>
       <c r="E368" t="n">
-        <v>-1.82</v>
+        <v>-1.66</v>
       </c>
       <c r="F368" t="n">
-        <v>107.4103469848633</v>
+        <v>42.72000122070312</v>
       </c>
       <c r="G368" t="n">
         <v>4.26</v>
       </c>
       <c r="H368" t="n">
-        <v>1.18384947727361</v>
+        <v>0.8116088396171504</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>1.47B</t>
+          <t>22.04B</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>40.90000152587891</v>
+        <v>102.8399963378906</v>
       </c>
       <c r="E369" t="n">
-        <v>-1.66</v>
+        <v>-1.82</v>
       </c>
       <c r="F369" t="n">
-        <v>42.72000122070312</v>
+        <v>107.4103469848633</v>
       </c>
       <c r="G369" t="n">
         <v>4.26</v>
       </c>
       <c r="H369" t="n">
-        <v>0.8116088396171504</v>
+        <v>1.18384947727361</v>
       </c>
     </row>
     <row r="370">
@@ -13952,65 +13948,65 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>DRTS</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>8.49B</t>
+          <t>870M</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>166.4700012207031</v>
+        <v>9.880000114440918</v>
       </c>
       <c r="E380" t="n">
         <v>-4.45</v>
       </c>
       <c r="F380" t="n">
-        <v>174.2299957275391</v>
+        <v>10.34000015258789</v>
       </c>
       <c r="G380" t="n">
         <v>4.45</v>
       </c>
       <c r="H380" t="n">
-        <v>0.7798176464415129</v>
+        <v>1.969255773007381</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>DRTS</t>
+          <t>CRUS</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>870M</t>
+          <t>8.49B</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>9.880000114440918</v>
+        <v>166.4700012207031</v>
       </c>
       <c r="E381" t="n">
         <v>-4.45</v>
       </c>
       <c r="F381" t="n">
-        <v>10.34000015258789</v>
+        <v>174.2299957275391</v>
       </c>
       <c r="G381" t="n">
         <v>4.45</v>
       </c>
       <c r="H381" t="n">
-        <v>1.969255773007381</v>
+        <v>0.7798176464415129</v>
       </c>
     </row>
     <row r="382">
@@ -14112,129 +14108,129 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>LGN</t>
+          <t>GILT</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>16.04B</t>
+          <t>1.50B</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>97.66000366210938</v>
+        <v>19.90999984741211</v>
       </c>
       <c r="E385" t="n">
-        <v>-0.49</v>
+        <v>-4.51</v>
       </c>
       <c r="F385" t="n">
-        <v>102.2699966430664</v>
+        <v>20.85000038146973</v>
       </c>
       <c r="G385" t="n">
         <v>4.51</v>
       </c>
       <c r="H385" t="n">
-        <v>0.9291546603854089</v>
+        <v>2.440145939312746</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>GILT</t>
+          <t>LGN</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>1.50B</t>
+          <t>16.04B</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>19.90999984741211</v>
+        <v>97.66000366210938</v>
       </c>
       <c r="E386" t="n">
-        <v>-4.51</v>
+        <v>-0.49</v>
       </c>
       <c r="F386" t="n">
-        <v>20.85000038146973</v>
+        <v>102.2699966430664</v>
       </c>
       <c r="G386" t="n">
         <v>4.51</v>
       </c>
       <c r="H386" t="n">
-        <v>2.440145939312746</v>
+        <v>0.9291546603854089</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>1.11B</t>
+          <t>875M</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>21.39999961853027</v>
+        <v>29.3799991607666</v>
       </c>
       <c r="E387" t="n">
-        <v>-0.7</v>
+        <v>-0.88</v>
       </c>
       <c r="F387" t="n">
-        <v>22.42000007629395</v>
+        <v>30.78164672851562</v>
       </c>
       <c r="G387" t="n">
         <v>4.55</v>
       </c>
       <c r="H387" t="n">
-        <v>0.6311540402220139</v>
+        <v>0.5364095766713611</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>875M</t>
+          <t>1.11B</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>29.3799991607666</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="E388" t="n">
-        <v>-0.88</v>
+        <v>-0.7</v>
       </c>
       <c r="F388" t="n">
-        <v>30.78164672851562</v>
+        <v>22.42000007629395</v>
       </c>
       <c r="G388" t="n">
         <v>4.55</v>
       </c>
       <c r="H388" t="n">
-        <v>0.5364095766713611</v>
+        <v>0.6311540402220139</v>
       </c>
     </row>
     <row r="389">
@@ -14368,65 +14364,65 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>TVTX</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>3.98B</t>
+          <t>141M</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>42.84000015258789</v>
+        <v>22.47999954223633</v>
       </c>
       <c r="E393" t="n">
-        <v>-1.54</v>
+        <v>0.63</v>
       </c>
       <c r="F393" t="n">
-        <v>44.90999984741211</v>
+        <v>23.56552505493164</v>
       </c>
       <c r="G393" t="n">
         <v>4.61</v>
       </c>
       <c r="H393" t="n">
-        <v>0.7976659327856663</v>
+        <v>0.4932650350977044</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>TVTX</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>141M</t>
+          <t>3.98B</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>22.47999954223633</v>
+        <v>42.84000015258789</v>
       </c>
       <c r="E394" t="n">
-        <v>0.63</v>
+        <v>-1.54</v>
       </c>
       <c r="F394" t="n">
-        <v>23.56552505493164</v>
+        <v>44.90999984741211</v>
       </c>
       <c r="G394" t="n">
         <v>4.61</v>
       </c>
       <c r="H394" t="n">
-        <v>0.4932650350977044</v>
+        <v>0.7976659327856663</v>
       </c>
     </row>
     <row r="395">
@@ -14548,7 +14544,7 @@
         <v>0.37</v>
       </c>
       <c r="F398" t="n">
-        <v>22.56417846679688</v>
+        <v>22.56418037414551</v>
       </c>
       <c r="G398" t="n">
         <v>4.67</v>
@@ -15072,193 +15068,193 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>LLYVK</t>
+          <t>URGN</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>8.92B</t>
+          <t>1.45B</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>96.93000030517578</v>
+        <v>29.79999923706055</v>
       </c>
       <c r="E415" t="n">
-        <v>1.41</v>
+        <v>-4.88</v>
       </c>
       <c r="F415" t="n">
-        <v>101.9049987792969</v>
+        <v>31.32999992370605</v>
       </c>
       <c r="G415" t="n">
         <v>4.88</v>
       </c>
       <c r="H415" t="n">
-        <v>0.8002049668716336</v>
+        <v>1.062328624344563</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>URGN</t>
+          <t>LLYVK</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>1.45B</t>
+          <t>8.92B</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>29.79999923706055</v>
+        <v>96.93000030517578</v>
       </c>
       <c r="E416" t="n">
-        <v>-4.88</v>
+        <v>1.41</v>
       </c>
       <c r="F416" t="n">
-        <v>31.32999992370605</v>
+        <v>101.9049987792969</v>
       </c>
       <c r="G416" t="n">
         <v>4.88</v>
       </c>
       <c r="H416" t="n">
-        <v>1.062328624344563</v>
+        <v>0.8002049668716336</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>PEBK</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>213M</t>
+          <t>70.40B</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>40.09000015258789</v>
+        <v>217.6699981689453</v>
       </c>
       <c r="E417" t="n">
-        <v>0.43</v>
+        <v>1.45</v>
       </c>
       <c r="F417" t="n">
-        <v>42.15999984741211</v>
+        <v>228.9100036621094</v>
       </c>
       <c r="G417" t="n">
         <v>4.91</v>
       </c>
       <c r="H417" t="n">
-        <v>0.9664261060558519</v>
+        <v>1.25186053091249</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>HFWA</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>214M</t>
+          <t>1.10B</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>30.20000076293945</v>
+        <v>26.75</v>
       </c>
       <c r="E418" t="n">
-        <v>2.13</v>
+        <v>-0.71</v>
       </c>
       <c r="F418" t="n">
-        <v>31.76000022888184</v>
+        <v>28.13249969482422</v>
       </c>
       <c r="G418" t="n">
         <v>4.91</v>
       </c>
       <c r="H418" t="n">
-        <v>1.386026817219478</v>
+        <v>0.8607604917504977</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>70.40B</t>
+          <t>213M</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>217.6699981689453</v>
+        <v>40.09000015258789</v>
       </c>
       <c r="E419" t="n">
-        <v>1.45</v>
+        <v>0.43</v>
       </c>
       <c r="F419" t="n">
-        <v>228.9100036621094</v>
+        <v>42.15999984741211</v>
       </c>
       <c r="G419" t="n">
         <v>4.91</v>
       </c>
       <c r="H419" t="n">
-        <v>1.25186053091249</v>
+        <v>0.9664261060558519</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>HFWA</t>
+          <t>RCMT</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>1.10B</t>
+          <t>214M</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>26.75</v>
+        <v>30.20000076293945</v>
       </c>
       <c r="E420" t="n">
-        <v>-0.71</v>
+        <v>2.13</v>
       </c>
       <c r="F420" t="n">
-        <v>28.13249969482422</v>
+        <v>31.76000022888184</v>
       </c>
       <c r="G420" t="n">
         <v>4.91</v>
       </c>
       <c r="H420" t="n">
-        <v>0.8607604917504977</v>
+        <v>1.386026817219478</v>
       </c>
     </row>
     <row r="421">
